--- a/MU.xlsx
+++ b/MU.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A261EC44-F124-4AF9-9615-A93ED2503C61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A341E0E6-5B6B-4F9A-AD99-7B967440A11D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="1950" windowWidth="38175" windowHeight="15240" xr2:uid="{E11AB79D-6789-46B9-A65D-613D2D1138C2}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{E11AB79D-6789-46B9-A65D-613D2D1138C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="46">
   <si>
     <t>MU</t>
   </si>
@@ -149,6 +149,33 @@
   <si>
     <t>Other (primarily NOR)</t>
   </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q125</t>
+  </si>
+  <si>
+    <t>Q225</t>
+  </si>
+  <si>
+    <t>Q325</t>
+  </si>
+  <si>
+    <t>Q425</t>
+  </si>
+  <si>
+    <t>Revenue Growth</t>
+  </si>
+  <si>
+    <t>Gross Margin</t>
+  </si>
+  <si>
+    <t>Operating Margin</t>
+  </si>
 </sst>
 </file>
 
@@ -159,13 +186,19 @@
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -195,6 +228,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -213,27 +253,35 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Per cent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -569,7 +617,9 @@
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.7109375" style="2" customWidth="1"/>
-    <col min="2" max="16384" width="9.140625" style="2"/>
+    <col min="2" max="7" width="9.140625" style="2"/>
+    <col min="8" max="8" width="9.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
@@ -585,7 +635,7 @@
         <v>4</v>
       </c>
       <c r="H2" s="3">
-        <v>97.8</v>
+        <v>989.6</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -593,10 +643,10 @@
         <v>5</v>
       </c>
       <c r="H3" s="4">
-        <v>1114.171932</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>10</v>
+        <v>1127.7340509999999</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -608,7 +658,7 @@
       </c>
       <c r="H4" s="4">
         <f>+H2*H3</f>
-        <v>108966.01494959999</v>
+        <v>1116005.6168696</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -619,11 +669,11 @@
         <v>7</v>
       </c>
       <c r="H5" s="4">
-        <f>6693+895+1156</f>
-        <v>8744</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>10</v>
+        <f>13908+681</f>
+        <v>14589</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -631,11 +681,11 @@
         <v>8</v>
       </c>
       <c r="H6" s="4">
-        <f>533+13252</f>
-        <v>13785</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>10</v>
+        <f>585+9557</f>
+        <v>10142</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -644,7 +694,7 @@
       </c>
       <c r="H7" s="4">
         <f>+H4-H5+H6</f>
-        <v>114007.01494959999</v>
+        <v>1111558.6168696</v>
       </c>
     </row>
   </sheetData>
@@ -692,6 +742,24 @@
       <c r="J2" s="5" t="s">
         <v>18</v>
       </c>
+      <c r="K2" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="O2" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="P2" s="11" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
@@ -709,11 +777,15 @@
         <v>6400</v>
       </c>
       <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
+      <c r="K3" s="7">
+        <v>6123</v>
+      </c>
       <c r="L3" s="7"/>
       <c r="M3" s="7"/>
       <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
+      <c r="O3" s="7">
+        <v>18768</v>
+      </c>
       <c r="P3" s="7"/>
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
@@ -760,11 +832,15 @@
         <v>2241</v>
       </c>
       <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
+      <c r="K4" s="7">
+        <v>1855</v>
+      </c>
       <c r="L4" s="7"/>
       <c r="M4" s="7"/>
       <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
+      <c r="O4" s="7">
+        <v>4997</v>
+      </c>
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
@@ -811,11 +887,15 @@
         <v>68</v>
       </c>
       <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
+      <c r="K5" s="7">
+        <v>75</v>
+      </c>
       <c r="L5" s="7"/>
       <c r="M5" s="7"/>
       <c r="N5" s="7"/>
-      <c r="O5" s="7"/>
+      <c r="O5" s="7">
+        <v>95</v>
+      </c>
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
@@ -862,12 +942,16 @@
         <v>8709</v>
       </c>
       <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
+      <c r="K6" s="8">
+        <v>8053</v>
+      </c>
       <c r="L6" s="7"/>
       <c r="M6" s="7"/>
       <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
+      <c r="O6" s="8">
+        <v>23860</v>
+      </c>
+      <c r="P6" s="8"/>
       <c r="Q6" s="7"/>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
@@ -913,11 +997,15 @@
         <v>5361</v>
       </c>
       <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
+      <c r="K7" s="7">
+        <v>5090</v>
+      </c>
       <c r="L7" s="7"/>
       <c r="M7" s="7"/>
       <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
+      <c r="O7" s="7">
+        <v>6105</v>
+      </c>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
@@ -965,7 +1053,7 @@
         <v>-35</v>
       </c>
       <c r="F8" s="7">
-        <f t="shared" ref="F8:J8" si="1">+F6-F7</f>
+        <f t="shared" ref="F8:Q8" si="1">+F6-F7</f>
         <v>0</v>
       </c>
       <c r="G8" s="7">
@@ -984,13 +1072,34 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="7"/>
+      <c r="K8" s="7">
+        <f t="shared" si="1"/>
+        <v>2963</v>
+      </c>
+      <c r="L8" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M8" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N8" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O8" s="7">
+        <f t="shared" ref="O8" si="2">+O6-O7</f>
+        <v>17755</v>
+      </c>
+      <c r="P8" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="R8" s="7"/>
       <c r="S8" s="7"/>
       <c r="T8" s="7"/>
@@ -1035,11 +1144,15 @@
         <v>888</v>
       </c>
       <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
+      <c r="K9" s="7">
+        <v>898</v>
+      </c>
       <c r="L9" s="7"/>
       <c r="M9" s="7"/>
       <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
+      <c r="O9" s="7">
+        <v>1250</v>
+      </c>
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
@@ -1086,11 +1199,15 @@
         <v>288</v>
       </c>
       <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
+      <c r="K10" s="7">
+        <v>285</v>
+      </c>
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
       <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
+      <c r="O10" s="7">
+        <v>344</v>
+      </c>
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
@@ -1137,11 +1254,15 @@
         <v>2</v>
       </c>
       <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
+      <c r="K11" s="7">
+        <v>-7</v>
+      </c>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
+      <c r="O11" s="7">
+        <v>-26</v>
+      </c>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
       <c r="R11" s="7"/>
@@ -1177,27 +1298,27 @@
         <v>25</v>
       </c>
       <c r="C12" s="7">
-        <f t="shared" ref="C12:H12" si="2">+C8-C9-C10+C11</f>
+        <f t="shared" ref="C12:H12" si="3">+C8-C9-C10+C11</f>
         <v>0</v>
       </c>
       <c r="D12" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E12" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-1128</v>
       </c>
       <c r="F12" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G12" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="H12" s="7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="I12" s="7">
@@ -1205,15 +1326,33 @@
         <v>2174</v>
       </c>
       <c r="J12" s="7">
-        <f t="shared" ref="J12" si="3">+J8-J9-J10+J11</f>
+        <f t="shared" ref="J12:P12" si="4">+J8-J9-J10+J11</f>
         <v>0</v>
       </c>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
+      <c r="K12" s="7">
+        <f t="shared" si="4"/>
+        <v>1773</v>
+      </c>
+      <c r="L12" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="M12" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="N12" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="O12" s="7">
+        <f>+O8-O9-O10+O11</f>
+        <v>16135</v>
+      </c>
+      <c r="P12" s="7">
+        <f>+P8-P9-P10+P11</f>
+        <v>0</v>
+      </c>
       <c r="Q12" s="7"/>
       <c r="R12" s="7"/>
       <c r="S12" s="7"/>
@@ -1259,11 +1398,15 @@
         <v>107</v>
       </c>
       <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
+      <c r="K13" s="7">
+        <v>108</v>
+      </c>
       <c r="L13" s="7"/>
       <c r="M13" s="7"/>
       <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
+      <c r="O13" s="7">
+        <v>155</v>
+      </c>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7"/>
@@ -1310,11 +1453,15 @@
         <v>118</v>
       </c>
       <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
+      <c r="K14" s="7">
+        <v>112</v>
+      </c>
       <c r="L14" s="7"/>
       <c r="M14" s="7"/>
       <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
+      <c r="O14" s="7">
+        <v>32</v>
+      </c>
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
       <c r="R14" s="7"/>
@@ -1361,11 +1508,15 @@
         <v>-11</v>
       </c>
       <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
+      <c r="K15" s="7">
+        <v>-11</v>
+      </c>
       <c r="L15" s="7"/>
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
+      <c r="O15" s="7">
+        <v>-98</v>
+      </c>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
       <c r="R15" s="7"/>
@@ -1401,27 +1552,27 @@
         <v>29</v>
       </c>
       <c r="C16" s="7">
-        <f t="shared" ref="C16:H16" si="4">+C12+C13-C14+C15</f>
+        <f t="shared" ref="C16:H16" si="5">+C12+C13-C14+C15</f>
         <v>0</v>
       </c>
       <c r="D16" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E16" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-1155</v>
       </c>
       <c r="F16" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G16" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H16" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="I16" s="7">
@@ -1429,15 +1580,33 @@
         <v>2152</v>
       </c>
       <c r="J16" s="7">
-        <f t="shared" ref="J16" si="5">+J12+J13-J14+J15</f>
+        <f t="shared" ref="J16:P16" si="6">+J12+J13-J14+J15</f>
         <v>0</v>
       </c>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
+      <c r="K16" s="7">
+        <f t="shared" si="6"/>
+        <v>1758</v>
+      </c>
+      <c r="L16" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="N16" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="7">
+        <f t="shared" ref="O16" si="7">+O12+O13-O14+O15</f>
+        <v>16160</v>
+      </c>
+      <c r="P16" s="7">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="Q16" s="7"/>
       <c r="R16" s="7"/>
       <c r="S16" s="7"/>
@@ -1483,11 +1652,15 @@
         <v>283</v>
       </c>
       <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
+      <c r="K17" s="7">
+        <v>177</v>
+      </c>
       <c r="L17" s="7"/>
       <c r="M17" s="7"/>
       <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
+      <c r="O17" s="7">
+        <v>2371</v>
+      </c>
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
       <c r="R17" s="7"/>
@@ -1534,11 +1707,15 @@
         <v>1</v>
       </c>
       <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
+      <c r="K18" s="7">
+        <v>2</v>
+      </c>
       <c r="L18" s="7"/>
       <c r="M18" s="7"/>
       <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
+      <c r="O18" s="7">
+        <v>-4</v>
+      </c>
       <c r="P18" s="7"/>
       <c r="Q18" s="7"/>
       <c r="R18" s="7"/>
@@ -1574,27 +1751,27 @@
         <v>32</v>
       </c>
       <c r="C19" s="7">
-        <f t="shared" ref="C19:H19" si="6">+C16-C17+C18</f>
+        <f t="shared" ref="C19:H19" si="8">+C16-C17+C18</f>
         <v>0</v>
       </c>
       <c r="D19" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="E19" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>-1234</v>
       </c>
       <c r="F19" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="G19" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="H19" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="I19" s="7">
@@ -1602,16 +1779,37 @@
         <v>1870</v>
       </c>
       <c r="J19" s="7">
-        <f t="shared" ref="J19" si="7">+J16-J17+J18</f>
+        <f t="shared" ref="J19:Q19" si="9">+J16-J17+J18</f>
         <v>0</v>
       </c>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="7"/>
-      <c r="P19" s="7"/>
-      <c r="Q19" s="7"/>
+      <c r="K19" s="7">
+        <f t="shared" si="9"/>
+        <v>1583</v>
+      </c>
+      <c r="L19" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="M19" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="N19" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="O19" s="7">
+        <f t="shared" ref="O19" si="10">+O16-O17+O18</f>
+        <v>13785</v>
+      </c>
+      <c r="P19" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="7">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="R19" s="7"/>
       <c r="S19" s="7"/>
       <c r="T19" s="7"/>
@@ -1689,11 +1887,11 @@
         <v>33</v>
       </c>
       <c r="C21" s="9" t="e">
-        <f t="shared" ref="C21:D21" si="8">+C19/C22</f>
+        <f t="shared" ref="C21:D21" si="11">+C19/C22</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D21" s="9" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E21" s="9">
@@ -1701,32 +1899,53 @@
         <v>-1.1218181818181818</v>
       </c>
       <c r="F21" s="9" t="e">
-        <f t="shared" ref="F21:J21" si="9">+F19/F22</f>
+        <f t="shared" ref="F21:Q21" si="12">+F19/F22</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G21" s="9" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H21" s="9" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I21" s="9">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>1.6831683168316831</v>
       </c>
       <c r="J21" s="9" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="7"/>
-      <c r="Q21" s="7"/>
+      <c r="K21" s="9">
+        <f t="shared" si="12"/>
+        <v>1.4197309417040358</v>
+      </c>
+      <c r="L21" s="9" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M21" s="9" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N21" s="9" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O21" s="9">
+        <f t="shared" ref="O21" si="13">+O19/O22</f>
+        <v>12.242451154529308</v>
+      </c>
+      <c r="P21" s="9" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q21" s="9" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="R21" s="7"/>
       <c r="S21" s="7"/>
       <c r="T21" s="7"/>
@@ -1771,11 +1990,15 @@
         <v>1111</v>
       </c>
       <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
+      <c r="K22" s="7">
+        <v>1115</v>
+      </c>
       <c r="L22" s="7"/>
       <c r="M22" s="7"/>
       <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
+      <c r="O22" s="7">
+        <v>1126</v>
+      </c>
       <c r="P22" s="7"/>
       <c r="Q22" s="7"/>
       <c r="R22" s="7"/>
@@ -1851,21 +2074,51 @@
       <c r="AR23" s="7"/>
     </row>
     <row r="24" spans="2:44" x14ac:dyDescent="0.2">
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="7"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="7"/>
+      <c r="B24" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="13">
+        <f>+I6/E6-1</f>
+        <v>0.84278459585272958</v>
+      </c>
+      <c r="J24" s="13" t="e">
+        <f t="shared" ref="J24:Q24" si="14">+J6/F6-1</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K24" s="13" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L24" s="13" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M24" s="13">
+        <f t="shared" si="14"/>
+        <v>-1</v>
+      </c>
+      <c r="N24" s="13" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O24" s="13">
+        <f t="shared" si="14"/>
+        <v>1.9628709797590962</v>
+      </c>
+      <c r="P24" s="13" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q24" s="13" t="e">
+        <f t="shared" si="14"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="R24" s="7"/>
       <c r="S24" s="7"/>
       <c r="T24" s="7"/>
@@ -1895,19 +2148,61 @@
       <c r="AR24" s="7"/>
     </row>
     <row r="25" spans="2:44" x14ac:dyDescent="0.2">
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="7"/>
-      <c r="O25" s="7"/>
+      <c r="B25" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="12" t="e">
+        <f t="shared" ref="C25:O25" si="15">+C8/C6</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D25" s="12" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E25" s="12">
+        <f t="shared" si="15"/>
+        <v>-7.4058400338552688E-3</v>
+      </c>
+      <c r="F25" s="12" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G25" s="12" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H25" s="12" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I25" s="12">
+        <f t="shared" si="15"/>
+        <v>0.38442990010334138</v>
+      </c>
+      <c r="J25" s="12" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K25" s="12">
+        <f t="shared" si="15"/>
+        <v>0.36793741462808893</v>
+      </c>
+      <c r="L25" s="12" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M25" s="12" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N25" s="12" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O25" s="12">
+        <f>+O8/O6</f>
+        <v>0.74413243922883487</v>
+      </c>
       <c r="P25" s="7"/>
       <c r="Q25" s="7"/>
       <c r="R25" s="7"/>
@@ -1939,19 +2234,61 @@
       <c r="AR25" s="7"/>
     </row>
     <row r="26" spans="2:44" x14ac:dyDescent="0.2">
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="7"/>
-      <c r="O26" s="7"/>
+      <c r="B26" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="12" t="e">
+        <f t="shared" ref="C26:O26" si="16">+C12/C6</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="D26" s="12" t="e">
+        <f t="shared" si="16"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E26" s="12">
+        <f t="shared" si="16"/>
+        <v>-0.23867964451967838</v>
+      </c>
+      <c r="F26" s="12" t="e">
+        <f t="shared" si="16"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G26" s="12" t="e">
+        <f t="shared" si="16"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H26" s="12" t="e">
+        <f t="shared" si="16"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I26" s="12">
+        <f t="shared" si="16"/>
+        <v>0.24962682282696061</v>
+      </c>
+      <c r="J26" s="12" t="e">
+        <f t="shared" si="16"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K26" s="12">
+        <f t="shared" si="16"/>
+        <v>0.22016639761579535</v>
+      </c>
+      <c r="L26" s="12" t="e">
+        <f t="shared" si="16"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M26" s="12" t="e">
+        <f t="shared" si="16"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N26" s="12" t="e">
+        <f t="shared" si="16"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O26" s="12">
+        <f>+O12/O6</f>
+        <v>0.67623637887678123</v>
+      </c>
       <c r="P26" s="7"/>
       <c r="Q26" s="7"/>
       <c r="R26" s="7"/>

--- a/MU.xlsx
+++ b/MU.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A341E0E6-5B6B-4F9A-AD99-7B967440A11D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CEECF23-51AA-43D5-A8AD-3E40A9B7CB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{E11AB79D-6789-46B9-A65D-613D2D1138C2}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="47">
   <si>
     <t>MU</t>
   </si>
@@ -176,6 +176,9 @@
   <si>
     <t>Operating Margin</t>
   </si>
+  <si>
+    <t>Q326</t>
+  </si>
 </sst>
 </file>
 
@@ -186,13 +189,19 @@
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -255,28 +264,31 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -635,7 +647,7 @@
         <v>4</v>
       </c>
       <c r="H2" s="3">
-        <v>989.6</v>
+        <v>1133.5</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -643,10 +655,10 @@
         <v>5</v>
       </c>
       <c r="H3" s="4">
-        <v>1127.7340509999999</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>37</v>
+        <v>1129.393151</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -658,7 +670,7 @@
       </c>
       <c r="H4" s="4">
         <f>+H2*H3</f>
-        <v>1116005.6168696</v>
+        <v>1280167.1366584999</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -669,11 +681,11 @@
         <v>7</v>
       </c>
       <c r="H5" s="4">
-        <f>13908+681</f>
-        <v>14589</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>37</v>
+        <f>24995+1027</f>
+        <v>26022</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -681,11 +693,11 @@
         <v>8</v>
       </c>
       <c r="H6" s="4">
-        <f>585+9557</f>
-        <v>10142</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>37</v>
+        <f>582+5140</f>
+        <v>5722</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -694,7 +706,7 @@
       </c>
       <c r="H7" s="4">
         <f>+H4-H5+H6</f>
-        <v>1111558.6168696</v>
+        <v>1259867.1366584999</v>
       </c>
     </row>
   </sheetData>
@@ -760,6 +772,9 @@
       <c r="P2" s="11" t="s">
         <v>38</v>
       </c>
+      <c r="Q2" s="14" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
@@ -777,17 +792,21 @@
         <v>6400</v>
       </c>
       <c r="J3" s="7"/>
-      <c r="K3" s="7">
+      <c r="K3" s="7"/>
+      <c r="L3" s="7">
         <v>6123</v>
       </c>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
+      <c r="M3" s="7">
+        <v>7071</v>
+      </c>
       <c r="N3" s="7"/>
-      <c r="O3" s="7">
+      <c r="O3" s="7"/>
+      <c r="P3" s="7">
         <v>18768</v>
       </c>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
+      <c r="Q3" s="7">
+        <v>31328</v>
+      </c>
       <c r="R3" s="7"/>
       <c r="S3" s="7"/>
       <c r="T3" s="7"/>
@@ -832,17 +851,21 @@
         <v>2241</v>
       </c>
       <c r="J4" s="7"/>
-      <c r="K4" s="7">
+      <c r="K4" s="7"/>
+      <c r="L4" s="7">
         <v>1855</v>
       </c>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
+      <c r="M4" s="7">
+        <v>2155</v>
+      </c>
       <c r="N4" s="7"/>
-      <c r="O4" s="7">
+      <c r="O4" s="7"/>
+      <c r="P4" s="7">
         <v>4997</v>
       </c>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
+      <c r="Q4" s="7">
+        <v>9943</v>
+      </c>
       <c r="R4" s="7"/>
       <c r="S4" s="7"/>
       <c r="T4" s="7"/>
@@ -887,17 +910,21 @@
         <v>68</v>
       </c>
       <c r="J5" s="7"/>
-      <c r="K5" s="7">
+      <c r="K5" s="7"/>
+      <c r="L5" s="7">
         <v>75</v>
       </c>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7"/>
+      <c r="M5" s="7">
+        <v>75</v>
+      </c>
       <c r="N5" s="7"/>
-      <c r="O5" s="7">
+      <c r="O5" s="7"/>
+      <c r="P5" s="7">
         <v>95</v>
       </c>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
+      <c r="Q5" s="7">
+        <v>185</v>
+      </c>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
       <c r="T5" s="7"/>
@@ -943,16 +970,24 @@
       </c>
       <c r="J6" s="8"/>
       <c r="K6" s="8">
+        <v>8709</v>
+      </c>
+      <c r="L6" s="8">
         <v>8053</v>
       </c>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
+      <c r="M6" s="8">
+        <v>9301</v>
+      </c>
       <c r="N6" s="7"/>
       <c r="O6" s="8">
+        <v>13643</v>
+      </c>
+      <c r="P6" s="8">
         <v>23860</v>
       </c>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="7"/>
+      <c r="Q6" s="8">
+        <v>41456</v>
+      </c>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
       <c r="T6" s="7"/>
@@ -998,16 +1033,24 @@
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7">
+        <v>5361</v>
+      </c>
+      <c r="L7" s="7">
         <v>5090</v>
       </c>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
+      <c r="M7" s="7">
+        <v>5793</v>
+      </c>
       <c r="N7" s="7"/>
       <c r="O7" s="7">
+        <v>5997</v>
+      </c>
+      <c r="P7" s="7">
         <v>6105</v>
       </c>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
+      <c r="Q7" s="7">
+        <v>6400</v>
+      </c>
       <c r="R7" s="7"/>
       <c r="S7" s="7"/>
       <c r="T7" s="7"/>
@@ -1074,31 +1117,31 @@
       </c>
       <c r="K8" s="7">
         <f t="shared" si="1"/>
+        <v>3348</v>
+      </c>
+      <c r="L8" s="7">
+        <f t="shared" ref="L8" si="2">+L6-L7</f>
         <v>2963</v>
-      </c>
-      <c r="L8" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
       </c>
       <c r="M8" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3508</v>
       </c>
       <c r="N8" s="7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O8" s="7">
-        <f t="shared" ref="O8" si="2">+O6-O7</f>
+        <f t="shared" ref="O8:P8" si="3">+O6-O7</f>
+        <v>7646</v>
+      </c>
+      <c r="P8" s="7">
+        <f t="shared" si="3"/>
         <v>17755</v>
-      </c>
-      <c r="P8" s="7">
-        <f t="shared" si="1"/>
-        <v>0</v>
       </c>
       <c r="Q8" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>35056</v>
       </c>
       <c r="R8" s="7"/>
       <c r="S8" s="7"/>
@@ -1145,16 +1188,24 @@
       </c>
       <c r="J9" s="7"/>
       <c r="K9" s="7">
+        <v>888</v>
+      </c>
+      <c r="L9" s="7">
         <v>898</v>
       </c>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
+      <c r="M9" s="7">
+        <v>965</v>
+      </c>
       <c r="N9" s="7"/>
       <c r="O9" s="7">
+        <v>1171</v>
+      </c>
+      <c r="P9" s="7">
         <v>1250</v>
       </c>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
+      <c r="Q9" s="7">
+        <v>1316</v>
+      </c>
       <c r="R9" s="7"/>
       <c r="S9" s="7"/>
       <c r="T9" s="7"/>
@@ -1200,16 +1251,24 @@
       </c>
       <c r="J10" s="7"/>
       <c r="K10" s="7">
+        <v>288</v>
+      </c>
+      <c r="L10" s="7">
         <v>285</v>
       </c>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
+      <c r="M10" s="7">
+        <v>318</v>
+      </c>
       <c r="N10" s="7"/>
       <c r="O10" s="7">
+        <v>337</v>
+      </c>
+      <c r="P10" s="7">
         <v>344</v>
       </c>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="7"/>
+      <c r="Q10" s="7">
+        <v>407</v>
+      </c>
       <c r="R10" s="7"/>
       <c r="S10" s="7"/>
       <c r="T10" s="7"/>
@@ -1255,16 +1314,24 @@
       </c>
       <c r="J11" s="7"/>
       <c r="K11" s="7">
+        <v>2</v>
+      </c>
+      <c r="L11" s="7">
         <v>-7</v>
       </c>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
+      <c r="M11" s="7">
+        <v>-56</v>
+      </c>
       <c r="N11" s="7"/>
       <c r="O11" s="7">
+        <v>-2</v>
+      </c>
+      <c r="P11" s="7">
         <v>-26</v>
       </c>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="7"/>
+      <c r="Q11" s="7">
+        <v>-15</v>
+      </c>
       <c r="R11" s="7"/>
       <c r="S11" s="7"/>
       <c r="T11" s="7"/>
@@ -1298,27 +1365,27 @@
         <v>25</v>
       </c>
       <c r="C12" s="7">
-        <f t="shared" ref="C12:H12" si="3">+C8-C9-C10+C11</f>
+        <f t="shared" ref="C12:H12" si="4">+C8-C9-C10+C11</f>
         <v>0</v>
       </c>
       <c r="D12" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="E12" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-1128</v>
       </c>
       <c r="F12" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G12" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H12" s="7">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="I12" s="7">
@@ -1326,34 +1393,37 @@
         <v>2174</v>
       </c>
       <c r="J12" s="7">
-        <f t="shared" ref="J12:P12" si="4">+J8-J9-J10+J11</f>
+        <f t="shared" ref="J12:N12" si="5">+J8-J9-J10+J11</f>
         <v>0</v>
       </c>
       <c r="K12" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
+        <v>2174</v>
+      </c>
+      <c r="L12" s="7">
+        <f t="shared" ref="L12" si="6">+L8-L9-L10+L11</f>
         <v>1773</v>
       </c>
-      <c r="L12" s="7">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
       <c r="M12" s="7">
-        <f t="shared" si="4"/>
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>2169</v>
       </c>
       <c r="N12" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O12" s="7">
         <f>+O8-O9-O10+O11</f>
-        <v>16135</v>
+        <v>6136</v>
       </c>
       <c r="P12" s="7">
         <f>+P8-P9-P10+P11</f>
-        <v>0</v>
-      </c>
-      <c r="Q12" s="7"/>
+        <v>16135</v>
+      </c>
+      <c r="Q12" s="7">
+        <f>+Q8-Q9-Q10+Q11</f>
+        <v>33318</v>
+      </c>
       <c r="R12" s="7"/>
       <c r="S12" s="7"/>
       <c r="T12" s="7"/>
@@ -1399,16 +1469,24 @@
       </c>
       <c r="J13" s="7"/>
       <c r="K13" s="7">
+        <v>107</v>
+      </c>
+      <c r="L13" s="7">
         <v>108</v>
       </c>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
+      <c r="M13" s="7">
+        <v>135</v>
+      </c>
       <c r="N13" s="7"/>
       <c r="O13" s="7">
+        <v>139</v>
+      </c>
+      <c r="P13" s="7">
         <v>155</v>
       </c>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
+      <c r="Q13" s="7">
+        <v>215</v>
+      </c>
       <c r="R13" s="7"/>
       <c r="S13" s="7"/>
       <c r="T13" s="7"/>
@@ -1454,16 +1532,24 @@
       </c>
       <c r="J14" s="7"/>
       <c r="K14" s="7">
+        <v>118</v>
+      </c>
+      <c r="L14" s="7">
         <v>112</v>
       </c>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
+      <c r="M14" s="7">
+        <v>123</v>
+      </c>
       <c r="N14" s="7"/>
       <c r="O14" s="7">
+        <v>74</v>
+      </c>
+      <c r="P14" s="7">
         <v>32</v>
       </c>
-      <c r="P14" s="7"/>
-      <c r="Q14" s="7"/>
+      <c r="Q14" s="7">
+        <v>0</v>
+      </c>
       <c r="R14" s="7"/>
       <c r="S14" s="7"/>
       <c r="T14" s="7"/>
@@ -1511,14 +1597,22 @@
       <c r="K15" s="7">
         <v>-11</v>
       </c>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
+      <c r="L15" s="7">
+        <v>-11</v>
+      </c>
+      <c r="M15" s="7">
+        <v>-68</v>
+      </c>
       <c r="N15" s="7"/>
       <c r="O15" s="7">
+        <v>-140</v>
+      </c>
+      <c r="P15" s="7">
         <v>-98</v>
       </c>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
+      <c r="Q15" s="7">
+        <v>-321</v>
+      </c>
       <c r="R15" s="7"/>
       <c r="S15" s="7"/>
       <c r="T15" s="7"/>
@@ -1552,27 +1646,27 @@
         <v>29</v>
       </c>
       <c r="C16" s="7">
-        <f t="shared" ref="C16:H16" si="5">+C12+C13-C14+C15</f>
+        <f t="shared" ref="C16:H16" si="7">+C12+C13-C14+C15</f>
         <v>0</v>
       </c>
       <c r="D16" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E16" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>-1155</v>
       </c>
       <c r="F16" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G16" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="H16" s="7">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="I16" s="7">
@@ -1580,34 +1674,37 @@
         <v>2152</v>
       </c>
       <c r="J16" s="7">
-        <f t="shared" ref="J16:P16" si="6">+J12+J13-J14+J15</f>
+        <f t="shared" ref="J16:Q16" si="8">+J12+J13-J14+J15</f>
         <v>0</v>
       </c>
       <c r="K16" s="7">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
+        <v>2152</v>
+      </c>
+      <c r="L16" s="7">
+        <f t="shared" ref="L16" si="9">+L12+L13-L14+L15</f>
         <v>1758</v>
       </c>
-      <c r="L16" s="7">
-        <f t="shared" si="6"/>
+      <c r="M16" s="7">
+        <f t="shared" si="8"/>
+        <v>2113</v>
+      </c>
+      <c r="N16" s="7">
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="M16" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="N16" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
       <c r="O16" s="7">
-        <f t="shared" ref="O16" si="7">+O12+O13-O14+O15</f>
+        <f t="shared" ref="O16:P16" si="10">+O12+O13-O14+O15</f>
+        <v>6061</v>
+      </c>
+      <c r="P16" s="7">
+        <f t="shared" si="10"/>
         <v>16160</v>
       </c>
-      <c r="P16" s="7">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="Q16" s="7"/>
+      <c r="Q16" s="7">
+        <f t="shared" si="8"/>
+        <v>33212</v>
+      </c>
       <c r="R16" s="7"/>
       <c r="S16" s="7"/>
       <c r="T16" s="7"/>
@@ -1653,16 +1750,24 @@
       </c>
       <c r="J17" s="7"/>
       <c r="K17" s="7">
+        <v>283</v>
+      </c>
+      <c r="L17" s="7">
         <v>177</v>
       </c>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
+      <c r="M17" s="7">
+        <v>235</v>
+      </c>
       <c r="N17" s="7"/>
       <c r="O17" s="7">
+        <v>829</v>
+      </c>
+      <c r="P17" s="7">
         <v>2371</v>
       </c>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="7"/>
+      <c r="Q17" s="7">
+        <v>4978</v>
+      </c>
       <c r="R17" s="7"/>
       <c r="S17" s="7"/>
       <c r="T17" s="7"/>
@@ -1708,16 +1813,24 @@
       </c>
       <c r="J18" s="7"/>
       <c r="K18" s="7">
+        <v>1</v>
+      </c>
+      <c r="L18" s="7">
         <v>2</v>
       </c>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
+      <c r="M18" s="7">
+        <v>7</v>
+      </c>
       <c r="N18" s="7"/>
       <c r="O18" s="7">
+        <v>8</v>
+      </c>
+      <c r="P18" s="7">
         <v>-4</v>
       </c>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="7"/>
+      <c r="Q18" s="7">
+        <v>9</v>
+      </c>
       <c r="R18" s="7"/>
       <c r="S18" s="7"/>
       <c r="T18" s="7"/>
@@ -1751,27 +1864,27 @@
         <v>32</v>
       </c>
       <c r="C19" s="7">
-        <f t="shared" ref="C19:H19" si="8">+C16-C17+C18</f>
+        <f t="shared" ref="C19:H19" si="11">+C16-C17+C18</f>
         <v>0</v>
       </c>
       <c r="D19" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="E19" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>-1234</v>
       </c>
       <c r="F19" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="G19" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="H19" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="I19" s="7">
@@ -1779,36 +1892,36 @@
         <v>1870</v>
       </c>
       <c r="J19" s="7">
-        <f t="shared" ref="J19:Q19" si="9">+J16-J17+J18</f>
+        <f t="shared" ref="J19:Q19" si="12">+J16-J17+J18</f>
         <v>0</v>
       </c>
       <c r="K19" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
+        <v>1870</v>
+      </c>
+      <c r="L19" s="7">
+        <f t="shared" ref="L19" si="13">+L16-L17+L18</f>
         <v>1583</v>
       </c>
-      <c r="L19" s="7">
-        <f t="shared" si="9"/>
+      <c r="M19" s="7">
+        <f t="shared" si="12"/>
+        <v>1885</v>
+      </c>
+      <c r="N19" s="7">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="M19" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="N19" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
       <c r="O19" s="7">
-        <f t="shared" ref="O19" si="10">+O16-O17+O18</f>
+        <f t="shared" ref="O19:P19" si="14">+O16-O17+O18</f>
+        <v>5240</v>
+      </c>
+      <c r="P19" s="7">
+        <f t="shared" si="14"/>
         <v>13785</v>
       </c>
-      <c r="P19" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
       <c r="Q19" s="7">
-        <f t="shared" si="9"/>
-        <v>0</v>
+        <f t="shared" si="12"/>
+        <v>28243</v>
       </c>
       <c r="R19" s="7"/>
       <c r="S19" s="7"/>
@@ -1887,11 +2000,11 @@
         <v>33</v>
       </c>
       <c r="C21" s="9" t="e">
-        <f t="shared" ref="C21:D21" si="11">+C19/C22</f>
+        <f t="shared" ref="C21:D21" si="15">+C19/C22</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D21" s="9" t="e">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E21" s="9">
@@ -1899,52 +2012,52 @@
         <v>-1.1218181818181818</v>
       </c>
       <c r="F21" s="9" t="e">
-        <f t="shared" ref="F21:Q21" si="12">+F19/F22</f>
+        <f t="shared" ref="F21:Q21" si="16">+F19/F22</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G21" s="9" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H21" s="9" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I21" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>1.6831683168316831</v>
       </c>
       <c r="J21" s="9" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K21" s="9">
-        <f t="shared" si="12"/>
-        <v>1.4197309417040358</v>
+        <f t="shared" si="16"/>
+        <v>1.6831683168316831</v>
       </c>
       <c r="L21" s="9" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M21" s="9" t="e">
-        <f t="shared" si="12"/>
+      <c r="M21" s="9">
+        <f t="shared" si="16"/>
+        <v>1.6860465116279071</v>
+      </c>
+      <c r="N21" s="9" t="e">
+        <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N21" s="9" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
       <c r="O21" s="9">
-        <f t="shared" ref="O21" si="13">+O19/O22</f>
+        <f t="shared" ref="O21" si="17">+O19/O22</f>
+        <v>4.6577777777777776</v>
+      </c>
+      <c r="P21" s="9">
+        <f t="shared" si="16"/>
         <v>12.242451154529308</v>
       </c>
-      <c r="P21" s="9" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q21" s="9" t="e">
-        <f t="shared" si="12"/>
-        <v>#DIV/0!</v>
+      <c r="Q21" s="9">
+        <f t="shared" si="16"/>
+        <v>25.038120567375888</v>
       </c>
       <c r="R21" s="7"/>
       <c r="S21" s="7"/>
@@ -1991,16 +2104,22 @@
       </c>
       <c r="J22" s="7"/>
       <c r="K22" s="7">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
+      <c r="M22" s="7">
+        <v>1118</v>
+      </c>
       <c r="N22" s="7"/>
       <c r="O22" s="7">
+        <v>1125</v>
+      </c>
+      <c r="P22" s="7">
         <v>1126</v>
       </c>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="7"/>
+      <c r="Q22" s="7">
+        <v>1128</v>
+      </c>
       <c r="R22" s="7"/>
       <c r="S22" s="7"/>
       <c r="T22" s="7"/>
@@ -2088,36 +2207,36 @@
         <v>0.84278459585272958</v>
       </c>
       <c r="J24" s="13" t="e">
-        <f t="shared" ref="J24:Q24" si="14">+J6/F6-1</f>
+        <f t="shared" ref="J24:Q24" si="18">+J6/F6-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K24" s="13" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="L24" s="13" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="M24" s="13">
-        <f t="shared" si="14"/>
-        <v>-1</v>
+        <f t="shared" si="18"/>
+        <v>6.7975657365943354E-2</v>
       </c>
       <c r="N24" s="13" t="e">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O24" s="13">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
+        <v>0.56654036054656109</v>
+      </c>
+      <c r="P24" s="13">
+        <f t="shared" si="18"/>
         <v>1.9628709797590962</v>
       </c>
-      <c r="P24" s="13" t="e">
-        <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q24" s="13" t="e">
-        <f t="shared" si="14"/>
-        <v>#DIV/0!</v>
+      <c r="Q24" s="13">
+        <f t="shared" si="18"/>
+        <v>3.457155144608107</v>
       </c>
       <c r="R24" s="7"/>
       <c r="S24" s="7"/>
@@ -2152,59 +2271,65 @@
         <v>44</v>
       </c>
       <c r="C25" s="12" t="e">
-        <f t="shared" ref="C25:O25" si="15">+C8/C6</f>
+        <f t="shared" ref="C25:N25" si="19">+C8/C6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D25" s="12" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E25" s="12">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>-7.4058400338552688E-3</v>
       </c>
       <c r="F25" s="12" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G25" s="12" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H25" s="12" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I25" s="12">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>0.38442990010334138</v>
       </c>
       <c r="J25" s="12" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K25" s="12">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
+        <v>0.38442990010334138</v>
+      </c>
+      <c r="L25" s="12">
+        <f t="shared" si="19"/>
         <v>0.36793741462808893</v>
       </c>
-      <c r="L25" s="12" t="e">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M25" s="12" t="e">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
+      <c r="M25" s="12">
+        <f t="shared" si="19"/>
+        <v>0.37716374583378132</v>
       </c>
       <c r="N25" s="12" t="e">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O25" s="12">
         <f>+O8/O6</f>
+        <v>0.56043392215788312</v>
+      </c>
+      <c r="P25" s="12">
+        <f t="shared" ref="P25:Q25" si="20">+P8/P6</f>
         <v>0.74413243922883487</v>
       </c>
-      <c r="P25" s="7"/>
-      <c r="Q25" s="7"/>
+      <c r="Q25" s="12">
+        <f t="shared" si="20"/>
+        <v>0.84561945194905441</v>
+      </c>
       <c r="R25" s="7"/>
       <c r="S25" s="7"/>
       <c r="T25" s="7"/>
@@ -2238,59 +2363,65 @@
         <v>45</v>
       </c>
       <c r="C26" s="12" t="e">
-        <f t="shared" ref="C26:O26" si="16">+C12/C6</f>
+        <f t="shared" ref="C26:N26" si="21">+C12/C6</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D26" s="12" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E26" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>-0.23867964451967838</v>
       </c>
       <c r="F26" s="12" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G26" s="12" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H26" s="12" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I26" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>0.24962682282696061</v>
       </c>
       <c r="J26" s="12" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="K26" s="12">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
+        <v>0.24962682282696061</v>
+      </c>
+      <c r="L26" s="12">
+        <f t="shared" si="21"/>
         <v>0.22016639761579535</v>
       </c>
-      <c r="L26" s="12" t="e">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M26" s="12" t="e">
-        <f t="shared" si="16"/>
-        <v>#DIV/0!</v>
+      <c r="M26" s="12">
+        <f t="shared" si="21"/>
+        <v>0.23320073110418235</v>
       </c>
       <c r="N26" s="12" t="e">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O26" s="12">
         <f>+O12/O6</f>
+        <v>0.44975445283295462</v>
+      </c>
+      <c r="P26" s="12">
+        <f t="shared" ref="P26:Q26" si="22">+P12/P6</f>
         <v>0.67623637887678123</v>
       </c>
-      <c r="P26" s="7"/>
-      <c r="Q26" s="7"/>
+      <c r="Q26" s="12">
+        <f t="shared" si="22"/>
+        <v>0.80369548436896954</v>
+      </c>
       <c r="R26" s="7"/>
       <c r="S26" s="7"/>
       <c r="T26" s="7"/>
